--- a/csv/model/FIC/formula_FIC_ON.xlsx
+++ b/csv/model/FIC/formula_FIC_ON.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -440,12 +440,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X371"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -11722,7 +11722,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -11892,7 +11892,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -12232,7 +12232,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -12402,7 +12402,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -12572,7 +12572,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -12657,7 +12657,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -12742,7 +12742,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -12912,7 +12912,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -13082,7 +13082,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -13422,7 +13422,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -13507,7 +13507,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -13677,7 +13677,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -13932,7 +13932,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -14017,7 +14017,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -14272,7 +14272,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -14612,7 +14612,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -14782,7 +14782,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -15037,7 +15037,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -15122,7 +15122,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -15207,7 +15207,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -15462,7 +15462,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -15547,7 +15547,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -15717,7 +15717,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -15802,7 +15802,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -15887,7 +15887,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -15972,7 +15972,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -16057,7 +16057,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -16142,7 +16142,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -16312,7 +16312,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -16482,7 +16482,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -16737,7 +16737,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -16822,7 +16822,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -16992,7 +16992,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -17077,7 +17077,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -17162,7 +17162,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -17247,7 +17247,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -17332,7 +17332,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -17502,7 +17502,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -17587,7 +17587,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -17672,7 +17672,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -17757,7 +17757,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -17842,7 +17842,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -17927,7 +17927,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -18012,7 +18012,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -18097,7 +18097,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -18267,7 +18267,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -18352,7 +18352,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -18437,7 +18437,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -18522,7 +18522,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -18607,7 +18607,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -18692,7 +18692,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -18777,7 +18777,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -18862,7 +18862,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -19117,7 +19117,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -19202,7 +19202,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -19287,7 +19287,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -19372,7 +19372,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -19457,7 +19457,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -19542,7 +19542,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -19627,7 +19627,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -19712,7 +19712,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -19797,7 +19797,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -19882,7 +19882,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -19967,7 +19967,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -20052,7 +20052,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -20137,7 +20137,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -20222,7 +20222,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -20307,7 +20307,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -20392,7 +20392,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -20482,7 +20482,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -20572,7 +20572,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -20662,7 +20662,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -20842,7 +20842,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -20932,7 +20932,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -21022,7 +21022,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -21112,7 +21112,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -21202,7 +21202,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -21292,7 +21292,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -21382,7 +21382,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -21742,7 +21742,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -21922,7 +21922,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -22012,7 +22012,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -22102,7 +22102,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -22192,7 +22192,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -22282,7 +22282,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -22372,7 +22372,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -22462,7 +22462,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -22552,7 +22552,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -22642,7 +22642,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -22732,7 +22732,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -22822,7 +22822,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -22912,7 +22912,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -23002,7 +23002,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -23092,7 +23092,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -23182,7 +23182,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -23272,7 +23272,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -23362,7 +23362,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -23452,7 +23452,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -23542,7 +23542,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -23632,7 +23632,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -23722,7 +23722,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -23812,7 +23812,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -23992,7 +23992,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -24082,7 +24082,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -24172,7 +24172,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -24262,7 +24262,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -24352,7 +24352,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -24442,7 +24442,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -24532,7 +24532,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -24622,7 +24622,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -24712,7 +24712,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -24802,7 +24802,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -24892,7 +24892,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -24982,7 +24982,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -25072,7 +25072,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -25162,7 +25162,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -25252,7 +25252,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -25342,7 +25342,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -25432,7 +25432,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -25522,7 +25522,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -25612,7 +25612,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -25702,7 +25702,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -25792,7 +25792,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -25882,7 +25882,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -25972,7 +25972,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -26062,7 +26062,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -26152,7 +26152,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -26242,7 +26242,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -26332,7 +26332,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -26422,7 +26422,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -26512,7 +26512,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -26602,7 +26602,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -26692,7 +26692,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -26782,7 +26782,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -26872,7 +26872,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
@@ -27052,7 +27052,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -27142,7 +27142,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -27232,7 +27232,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -27322,7 +27322,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -27412,7 +27412,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
@@ -27502,7 +27502,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -27592,7 +27592,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -27682,7 +27682,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -27772,7 +27772,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -27862,7 +27862,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -27947,7 +27947,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -28032,7 +28032,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -28117,7 +28117,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -28202,7 +28202,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -28287,7 +28287,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -28372,7 +28372,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -28457,7 +28457,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -28542,7 +28542,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -28627,7 +28627,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -28712,7 +28712,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
@@ -28797,7 +28797,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -28882,7 +28882,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -28967,7 +28967,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -29052,7 +29052,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -29137,7 +29137,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -29222,7 +29222,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -29307,7 +29307,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -29392,7 +29392,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -29477,7 +29477,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -29562,7 +29562,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -29647,7 +29647,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -29732,7 +29732,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -29817,7 +29817,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -29902,7 +29902,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -29987,7 +29987,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
@@ -30072,7 +30072,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -30157,7 +30157,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -30242,7 +30242,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
@@ -30327,7 +30327,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -30412,7 +30412,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
@@ -30497,7 +30497,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -30582,7 +30582,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
@@ -30667,7 +30667,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -30752,7 +30752,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
@@ -30837,7 +30837,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
@@ -30922,7 +30922,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
@@ -31007,7 +31007,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -31092,7 +31092,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -31177,7 +31177,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -31262,7 +31262,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
@@ -31347,7 +31347,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
@@ -31432,7 +31432,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -31517,7 +31517,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -31597,7 +31597,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -31672,7 +31672,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
@@ -31747,7 +31747,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -31822,7 +31822,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -31897,7 +31897,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -31972,7 +31972,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -32052,7 +32052,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -32137,7 +32137,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -32222,7 +32222,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
